--- a/hpi_scraper/Technographic/coresignal/coresignal_api_report.xlsx
+++ b/hpi_scraper/Technographic/coresignal/coresignal_api_report.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2.354 avg</t>
+          <t>1.283 avg</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">

--- a/hpi_scraper/Technographic/coresignal/coresignal_api_report.xlsx
+++ b/hpi_scraper/Technographic/coresignal/coresignal_api_report.xlsx
@@ -449,15 +449,15 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
+    <col width="72" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Estimated 2 Collect credits (1 successful enrich x 2)</t>
+          <t>1 successful company enrich response; estimated 2 Coresignal collect credits.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -564,15 +564,11 @@
           <t>ratelimit-limit: 18; ratelimit-remaining: 17; ratelimit-reset: 1; x-ratelimit-limit-second: 18; x-ratelimit-remaining-second: 17</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -584,19 +580,17 @@
           <t>200:1</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K2" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Y - it_spend_estimate</t>
+          <t>Partial - technologies were returned, but IT spend was not available from this endpoint.</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Coresignal enrich returns technologies_used with first/last verification dates, but does not return IT spend estimate in this response.</t>
+          <t>Good source for named technologies with provider verification dates. IT spend needs another provider or manual research.</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
